--- a/Team-Data/2014-15/4-5-2014-15.xlsx
+++ b/Team-Data/2014-15/4-5-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -766,13 +833,13 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -799,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -933,16 +1000,16 @@
         <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
@@ -1121,7 +1188,7 @@
         <v>17</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>15</v>
@@ -1148,7 +1215,7 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
@@ -1318,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>8</v>
@@ -1348,10 +1415,10 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
         <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1413,43 +1480,43 @@
         <v>0.442</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
         <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O6" t="n">
         <v>19.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.785</v>
       </c>
       <c r="R6" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S6" t="n">
         <v>33.9</v>
       </c>
       <c r="T6" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="U6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V6" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W6" t="n">
         <v>6.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y6" t="n">
         <v>5.4</v>
@@ -1461,22 +1528,22 @@
         <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1509,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1530,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.649</v>
+        <v>0.645</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J7" t="n">
         <v>82.2</v>
@@ -1595,28 +1662,28 @@
         <v>0.459</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M7" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P7" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
         <v>42.9</v>
@@ -1643,16 +1710,16 @@
         <v>20.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC7" t="n">
         <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1661,25 +1728,25 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1688,16 +1755,16 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -1706,16 +1773,16 @@
         <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
         <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.605</v>
+        <v>0.597</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,13 +1838,13 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M8" t="n">
         <v>25.6</v>
@@ -1789,19 +1856,19 @@
         <v>16.8</v>
       </c>
       <c r="P8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.4</v>
@@ -1822,7 +1889,7 @@
         <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
         <v>104.6</v>
@@ -1831,19 +1898,19 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1870,13 +1937,13 @@
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1885,7 +1952,7 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-4</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2046,7 +2113,7 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
@@ -2073,7 +2140,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2219,7 +2286,7 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="n">
         <v>10</v>
@@ -2228,7 +2295,7 @@
         <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" t="n">
         <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2329,25 +2396,25 @@
         <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.395</v>
+        <v>0.397</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
         <v>27.4</v>
@@ -2368,16 +2435,16 @@
         <v>19.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.7</v>
+        <v>109.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2410,19 +2477,19 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR11" t="n">
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>5</v>
@@ -2431,13 +2498,13 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -2496,13 +2563,13 @@
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
         <v>11.5</v>
@@ -2511,16 +2578,16 @@
         <v>33.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P12" t="n">
         <v>25.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.721</v>
       </c>
       <c r="R12" t="n">
         <v>11.9</v>
@@ -2538,7 +2605,7 @@
         <v>16.8</v>
       </c>
       <c r="W12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
@@ -2547,19 +2614,19 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
         <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>3</v>
@@ -2580,7 +2647,7 @@
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2607,7 +2674,7 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
@@ -2628,7 +2695,7 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="n">
         <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.442</v>
+        <v>0.434</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2687,37 +2754,37 @@
         <v>0.438</v>
       </c>
       <c r="L13" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O13" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
         <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U13" t="n">
         <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W13" t="n">
         <v>6.2</v>
@@ -2735,25 +2802,25 @@
         <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2771,19 +2838,19 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
         <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
@@ -2792,7 +2859,7 @@
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
         <v>15</v>
@@ -2804,19 +2871,19 @@
         <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,28 +2930,28 @@
         <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M14" t="n">
         <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O14" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P14" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.708</v>
+        <v>0.709</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
@@ -2899,13 +2966,13 @@
         <v>24.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W14" t="n">
         <v>7.8</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -2914,19 +2981,19 @@
         <v>21.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB14" t="n">
         <v>106.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2938,10 +3005,10 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2983,7 +3050,7 @@
         <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -3045,28 +3112,28 @@
         <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="K15" t="n">
         <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
@@ -3078,10 +3145,10 @@
         <v>44</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W15" t="n">
         <v>7.2</v>
@@ -3093,16 +3160,16 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
         <v>29</v>
@@ -3123,7 +3190,7 @@
         <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>25</v>
@@ -3135,16 +3202,16 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
@@ -3153,10 +3220,10 @@
         <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3165,13 +3232,13 @@
         <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,10 +3369,10 @@
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
         <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>0.442</v>
+        <v>0.447</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3415,25 +3482,25 @@
         <v>0.456</v>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
         <v>20.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
         <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
         <v>29.8</v>
@@ -3442,7 +3509,7 @@
         <v>38.7</v>
       </c>
       <c r="U17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
         <v>15</v>
@@ -3457,31 +3524,31 @@
         <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3499,10 +3566,10 @@
         <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3523,10 +3590,10 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>22</v>
@@ -3535,10 +3602,10 @@
         <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3684,7 +3751,7 @@
         <v>8</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>25</v>
@@ -3711,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG19" t="n">
         <v>29</v>
@@ -3851,7 +3918,7 @@
         <v>24</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3875,7 +3942,7 @@
         <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3893,10 +3960,10 @@
         <v>9</v>
       </c>
       <c r="AX19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY19" t="n">
         <v>27</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>26</v>
       </c>
       <c r="AZ19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.533</v>
+        <v>0.539</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,10 +4022,10 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7.2</v>
@@ -3967,25 +4034,25 @@
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O20" t="n">
         <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.761</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22.1</v>
@@ -3997,31 +4064,31 @@
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
@@ -4033,10 +4100,10 @@
         <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4051,19 +4118,19 @@
         <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
         <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>0.195</v>
+        <v>0.184</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,49 +4204,49 @@
         <v>35.2</v>
       </c>
       <c r="J21" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L21" t="n">
         <v>6.8</v>
       </c>
       <c r="M21" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O21" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="P21" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V21" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
         <v>4.4</v>
@@ -4188,16 +4255,16 @@
         <v>21.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.4</v>
+        <v>-9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4209,25 +4276,25 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4251,13 +4318,13 @@
         <v>19</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>7</v>
@@ -4266,7 +4333,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" t="n">
         <v>42</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>0.545</v>
+        <v>0.553</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,19 +4386,19 @@
         <v>38.6</v>
       </c>
       <c r="J22" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K22" t="n">
         <v>0.447</v>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M22" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="O22" t="n">
         <v>18.7</v>
@@ -4340,7 +4407,7 @@
         <v>24.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R22" t="n">
         <v>12.6</v>
@@ -4349,13 +4416,13 @@
         <v>34.9</v>
       </c>
       <c r="T22" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="U22" t="n">
         <v>20.7</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W22" t="n">
         <v>7.2</v>
@@ -4367,19 +4434,19 @@
         <v>4.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC22" t="n">
         <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4391,7 +4458,7 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4433,7 +4500,7 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -4483,40 +4550,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
         <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.316</v>
+        <v>0.312</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
         <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
         <v>19.1</v>
@@ -4525,43 +4592,43 @@
         <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>15</v>
@@ -4582,10 +4649,10 @@
         <v>18</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4603,16 +4670,16 @@
         <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
         <v>25</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J24" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="L24" t="n">
         <v>8.4</v>
       </c>
       <c r="M24" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N24" t="n">
         <v>0.324</v>
       </c>
       <c r="O24" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.67</v>
       </c>
       <c r="R24" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U24" t="n">
         <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="W24" t="n">
         <v>9.699999999999999</v>
@@ -4728,7 +4795,7 @@
         <v>6.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z24" t="n">
         <v>21.5</v>
@@ -4761,22 +4828,22 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN24" t="n">
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>10</v>
@@ -4785,13 +4852,13 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>25</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
         <v>9</v>
@@ -4973,13 +5040,13 @@
         <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
         <v>6</v>
@@ -5000,7 +5067,7 @@
         <v>8</v>
       </c>
       <c r="BC25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
@@ -5119,25 +5186,25 @@
         <v>6</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK26" t="n">
         <v>17</v>
       </c>
       <c r="AL26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5158,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5167,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,10 +5243,10 @@
         <v>2</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
-        <v>0.342</v>
+        <v>0.347</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L27" t="n">
         <v>5.5</v>
@@ -5244,34 +5311,34 @@
         <v>0.339</v>
       </c>
       <c r="O27" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="P27" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R27" t="n">
         <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U27" t="n">
         <v>20.1</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W27" t="n">
         <v>6.6</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
@@ -5289,13 +5356,13 @@
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5328,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -5408,28 +5475,28 @@
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.464</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O28" t="n">
         <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0.779</v>
@@ -5438,40 +5505,40 @@
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB28" t="n">
         <v>102.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5486,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
         <v>12</v>
@@ -5501,34 +5568,34 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
       </c>
       <c r="AV28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW28" t="n">
         <v>11</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5543,7 +5610,7 @@
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5665,7 +5732,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5704,10 +5771,10 @@
         <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>18</v>
@@ -5719,7 +5786,7 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
         <v>42</v>
       </c>
       <c r="G30" t="n">
-        <v>0.455</v>
+        <v>0.447</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J30" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L30" t="n">
         <v>7.3</v>
@@ -5793,7 +5860,7 @@
         <v>16.9</v>
       </c>
       <c r="P30" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0.723</v>
@@ -5805,16 +5872,16 @@
         <v>31.9</v>
       </c>
       <c r="T30" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U30" t="n">
         <v>19.8</v>
       </c>
       <c r="V30" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X30" t="n">
         <v>6</v>
@@ -5829,22 +5896,22 @@
         <v>19.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC30" t="n">
         <v>0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5859,7 +5926,7 @@
         <v>19</v>
       </c>
       <c r="AL30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
@@ -5889,13 +5956,13 @@
         <v>30</v>
       </c>
       <c r="AV30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW30" t="n">
         <v>17</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,13 +6096,13 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI31" t="n">
         <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
         <v>5</v>
@@ -6050,19 +6117,19 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
         <v>23</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6071,19 +6138,19 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-5-2014-15</t>
+          <t>2015-04-05</t>
         </is>
       </c>
     </row>
